--- a/sprint_1/1_business_analysis/deliverables/AC1.xlsx
+++ b/sprint_1/1_business_analysis/deliverables/AC1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8987"/>
+    <workbookView windowWidth="23040" windowHeight="9707"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
   <si>
     <t>Case nghiệp vụ</t>
   </si>
@@ -107,7 +107,7 @@
     <t>Water</t>
   </si>
   <si>
-    <t xml:space="preserve">The total number of real-time environmental water quality monitoring stations </t>
+    <t>Number of real-time environmental water quality monitoring stations per 100,000 population</t>
   </si>
   <si>
     <t>Rác thải rắn</t>
@@ -122,7 +122,7 @@
     <t>Percentage of public garbage bins that are sensor-enabled public garbage bins</t>
   </si>
   <si>
-    <t>Percentage of waste management vehicles equipped with smart waste management system</t>
+    <t>Percentage of waste collection centers equipped with telemetering</t>
   </si>
   <si>
     <t>Năng lượng</t>
@@ -142,6 +142,9 @@
   </si>
   <si>
     <t>Percentage of traffic lights that are intelligent/smart</t>
+  </si>
+  <si>
+    <t>Percentage of city area mapped with real-time interactive map system</t>
   </si>
   <si>
     <t>An ninh</t>
@@ -553,7 +556,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -571,6 +574,68 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -700,7 +765,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -712,34 +777,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -824,7 +889,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -835,27 +900,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1391,7 +1465,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14.1111111111111" customWidth="1"/>
@@ -1406,317 +1480,369 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
+      <c r="B1" s="2"/>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" ht="36" spans="1:6">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
+      <c r="E2" s="5">
+        <v>7.1</v>
+      </c>
+      <c r="F2" s="6"/>
     </row>
     <row r="3" ht="36" spans="1:6">
-      <c r="A3" s="9"/>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8"/>
+      <c r="E3" s="5">
+        <v>19.8</v>
+      </c>
+      <c r="F3" s="6"/>
     </row>
     <row r="4" ht="36" spans="1:6">
-      <c r="A4" s="9"/>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8"/>
+      <c r="E4" s="5">
+        <v>12.1</v>
+      </c>
+      <c r="F4" s="6"/>
     </row>
     <row r="5" ht="36" spans="1:6">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="6" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8"/>
+      <c r="E5" s="5">
+        <v>12.2</v>
+      </c>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" ht="36" spans="1:6">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="6" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8"/>
+      <c r="E6" s="5">
+        <v>8.3</v>
+      </c>
+      <c r="F6" s="6"/>
     </row>
     <row r="7" ht="36" spans="1:6">
-      <c r="A7" s="9"/>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8"/>
+      <c r="E7" s="5">
+        <v>7.6</v>
+      </c>
+      <c r="F7" s="6"/>
     </row>
     <row r="8" ht="36" spans="1:6">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="6" t="s">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8"/>
+      <c r="E8" s="5">
+        <v>7.7</v>
+      </c>
+      <c r="F8" s="6"/>
     </row>
     <row r="9" ht="54" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8"/>
-    </row>
-    <row r="10" ht="36" spans="1:6">
-      <c r="A10" s="9"/>
-      <c r="B10" s="6" t="s">
+      <c r="E9" s="5">
+        <v>8.2</v>
+      </c>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" ht="54" spans="1:6">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8"/>
+      <c r="E10" s="5">
+        <v>23.2</v>
+      </c>
+      <c r="F10" s="6"/>
     </row>
     <row r="11" ht="72" spans="1:6">
-      <c r="A11" s="9"/>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8"/>
+      <c r="E11" s="5">
+        <v>16.2</v>
+      </c>
+      <c r="F11" s="6"/>
     </row>
     <row r="12" ht="36" spans="1:6">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="6" t="s">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8"/>
-    </row>
-    <row r="13" ht="54" spans="1:6">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="6" t="s">
+      <c r="E12" s="5">
+        <v>16.5</v>
+      </c>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" ht="36" spans="1:6">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8"/>
+      <c r="E13" s="5">
+        <v>16.1</v>
+      </c>
+      <c r="F13" s="6"/>
     </row>
     <row r="14" ht="54" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="6" t="s">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8"/>
+      <c r="E14" s="5">
+        <v>7.4</v>
+      </c>
+      <c r="F14" s="6"/>
     </row>
     <row r="15" ht="36" spans="1:6">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="6" t="s">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="8"/>
+      <c r="E15" s="5">
+        <v>7.5</v>
+      </c>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" ht="36" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="8" t="s">
         <v>35</v>
       </c>
       <c r="B16" s="9"/>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="8"/>
+      <c r="E16" s="5">
+        <v>19.3</v>
+      </c>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" ht="36" spans="1:6">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="6" t="s">
+      <c r="A17" s="10"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="8"/>
+      <c r="E17" s="5">
+        <v>19.9</v>
+      </c>
+      <c r="F17" s="6"/>
     </row>
     <row r="18" ht="36" spans="1:6">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="12"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="6" t="s">
+      <c r="E18" s="5">
+        <v>19.1</v>
+      </c>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" ht="36" spans="1:6">
+      <c r="A19" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="8"/>
-    </row>
-    <row r="19" ht="18" spans="1:6">
-      <c r="A19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="E19" s="5">
+        <v>15.1</v>
+      </c>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" ht="18" spans="1:6">
+      <c r="A20" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="8"/>
-    </row>
-    <row r="20" ht="18" spans="1:6">
-      <c r="A20" s="9"/>
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="D20" s="4"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" ht="18" spans="1:6">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="8"/>
-    </row>
-    <row r="21" ht="18" spans="1:6">
-      <c r="A21" s="9"/>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="D21" s="4"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" ht="18" spans="1:6">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="8"/>
-    </row>
-    <row r="22" ht="18" spans="1:6">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="8"/>
-    </row>
-    <row r="23" ht="36" spans="1:6">
-      <c r="A23" s="9"/>
-      <c r="B23" s="6" t="s">
+      <c r="D22" s="4"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" ht="18" spans="1:6">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" s="4"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" ht="36" spans="1:6">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="8"/>
+      <c r="C24" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="11">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
     <mergeCell ref="A2:A8"/>
     <mergeCell ref="A9:A13"/>
-    <mergeCell ref="A19:A23"/>
+    <mergeCell ref="A20:A24"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B11:B13"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="B22:B23"/>
     <mergeCell ref="A14:B15"/>
-    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="A16:B18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/sprint_1/1_business_analysis/deliverables/AC1.xlsx
+++ b/sprint_1/1_business_analysis/deliverables/AC1.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9707"/>
+    <workbookView windowWidth="11520" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="96">
   <si>
     <t>Case nghiệp vụ</t>
   </si>
@@ -184,6 +185,138 @@
   </si>
   <si>
     <t>Population and Social Conditions</t>
+  </si>
+  <si>
+    <t>AC234 – Smart City Chatbot Questions (SNI ISO 37122:2019)</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Câu hỏi</t>
+  </si>
+  <si>
+    <t>ISO 37122 ID</t>
+  </si>
+  <si>
+    <t>Phân loại Truy vấn (AC3)</t>
+  </si>
+  <si>
+    <t>ESG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHẦN 1: CÂU HỎI CHO CƯ DÂN (RESIDENT) </t>
+  </si>
+  <si>
+    <t>Kiếm trạm sạc xe điện gần [vị trí]</t>
+  </si>
+  <si>
+    <t>Tầm [thời gian] thì còn nhiều chỗ sạc xe điện không</t>
+  </si>
+  <si>
+    <t>Giờ nào thì nhu cầu sử dụng trạm sạc nhiều nhất</t>
+  </si>
+  <si>
+    <t>Kiếm bãi xe còn trống gần [vị trí]</t>
+  </si>
+  <si>
+    <t>Bãi xe [tên/vị trí] còn chỗ trống không</t>
+  </si>
+  <si>
+    <t>Số liệu tiêu thụ điện của hộ gia đình tôi trong [số] tháng qua?</t>
+  </si>
+  <si>
+    <t>Số liệu tiêu thụ nước của hộ gia đình tôi trong [số] tháng qua?</t>
+  </si>
+  <si>
+    <t>Tòa nhà [tên/vị trí] đang được trang bị các thiết bị thông minh gì?</t>
+  </si>
+  <si>
+    <t>Percentage of houses with smart energy meters + Percentage of houses with smart water meters</t>
+  </si>
+  <si>
+    <t>12.1 + 12.2</t>
+  </si>
+  <si>
+    <t>Tòa nhà [tên/vị trí] có thiết bị lọc/kiểm tra không khí trong nhà không?</t>
+  </si>
+  <si>
+    <t>Chất lượng không khí hiện tại ở tòa nhà [tên/vị trí]</t>
+  </si>
+  <si>
+    <t>[Nhiệt độ/độ ẩm/thời tiết] tại [địa điểm]</t>
+  </si>
+  <si>
+    <t>PHẦN 2: CÂU HỎI CHO QUẢN LÝ THÀNH PHỐ (CITY MANAGER)</t>
+  </si>
+  <si>
+    <t>Tỉ lệ trạm sạc hiện tại so với số lượng xe điện cư dân đã đăng ký</t>
+  </si>
+  <si>
+    <t>Danh sách các trạm sạc không hoạt động / bị hư</t>
+  </si>
+  <si>
+    <t>Top [số] khu vực có nhu cầu sử dụng trạm sạc [cao/thấp]</t>
+  </si>
+  <si>
+    <t>Tỉ lệ chỗ đậu xe so với số lượng xe cư dân đã đăng ký</t>
+  </si>
+  <si>
+    <t>Top [số] bãi xe được sử dụng [ít/nhiều] nhất</t>
+  </si>
+  <si>
+    <t>Danh sách các thiết bị thông minh lắp đặt trong nhà bị hư hỏng</t>
+  </si>
+  <si>
+    <t>Danh sách các thiết bị thông minh lắp đặt ngoài trời bị hư hỏng</t>
+  </si>
+  <si>
+    <t>Phát thông báo dọn rác cho nhân viên khi có thùng rác đầy</t>
+  </si>
+  <si>
+    <t>Percentage of the city population that has a door-to-door garbage collection with an individual monitoring of household waste quantities + Percentage of public garbage bins that are sensor-enabled public garbage bins</t>
+  </si>
+  <si>
+    <t>16.2 + 16.5</t>
+  </si>
+  <si>
+    <t>Số lượng thùng rác thông minh được lắp đặt theo khu vực</t>
+  </si>
+  <si>
+    <t>Tỷ trọng/số liệu điện năng của các nguồn cấp điện</t>
+  </si>
+  <si>
+    <t>Percentage of the city’s electricity that is produced using distributed generation production systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lượng điện tiêu thụ tại [khu vực] </t>
+  </si>
+  <si>
+    <t>Số liệu/xu hướng sử dụng điện tại [khu vực] trong [số] [ngày/tuần/tháng/năm] qua</t>
+  </si>
+  <si>
+    <t>Top [số] khu vực tiêu thụ điện [nhiều/ít] nhất</t>
+  </si>
+  <si>
+    <t>Tỉ lệ khả năng lưu trữ của mạng lưới điện hiện tại so với tổng lượng điện tiêu thụ</t>
+  </si>
+  <si>
+    <t>Số lượng đèn tín hiệu giao thông thông minh hiện tại, lọc theo trạng thái (hoạt động bình thường/hư hỏng)</t>
+  </si>
+  <si>
+    <t>Danh sách các đèn báo hiệu giao thông thông minh gặp vấn đề, bị hỏng.</t>
+  </si>
+  <si>
+    <t>Các tuyến đường đang ùn tắc hiện tại</t>
+  </si>
+  <si>
+    <t>Giờ cao điểm của các tuyến đường</t>
+  </si>
+  <si>
+    <t>Danh sách các camera đang gặp vấn đề, bị hỏng, không hoạt động</t>
+  </si>
+  <si>
+    <t>Số lượng camera theo khu vực</t>
   </si>
 </sst>
 </file>
@@ -196,7 +329,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -207,11 +340,17 @@
     <font>
       <b/>
       <sz val="14"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -759,137 +898,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -899,20 +1038,54 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1472,363 +1645,363 @@
     <col min="2" max="2" width="28.8888888888889" customWidth="1"/>
     <col min="3" max="3" width="24.6388888888889" customWidth="1"/>
     <col min="4" max="4" width="47.4722222222222" customWidth="1"/>
-    <col min="5" max="5" width="16.3611111111111" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.3611111111111" style="16" customWidth="1"/>
     <col min="6" max="6" width="43.4351851851852" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.4" spans="1:6">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="18" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" ht="36" spans="1:6">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="10">
         <v>7.1</v>
       </c>
-      <c r="F2" s="6"/>
+      <c r="F2" s="19"/>
     </row>
     <row r="3" ht="36" spans="1:6">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="10">
         <v>19.8</v>
       </c>
-      <c r="F3" s="6"/>
+      <c r="F3" s="19"/>
     </row>
     <row r="4" ht="36" spans="1:6">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="10">
         <v>12.1</v>
       </c>
-      <c r="F4" s="6"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" ht="36" spans="1:6">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="7" t="s">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="10">
         <v>12.2</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F5" s="19"/>
     </row>
     <row r="6" ht="36" spans="1:6">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4" t="s">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="10">
         <v>8.3</v>
       </c>
-      <c r="F6" s="6"/>
+      <c r="F6" s="19"/>
     </row>
     <row r="7" ht="36" spans="1:6">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4" t="s">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="10">
         <v>7.6</v>
       </c>
-      <c r="F7" s="6"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" ht="36" spans="1:6">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4" t="s">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="10">
         <v>7.7</v>
       </c>
-      <c r="F8" s="6"/>
+      <c r="F8" s="19"/>
     </row>
     <row r="9" ht="54" spans="1:6">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="10">
         <v>8.2</v>
       </c>
-      <c r="F9" s="6"/>
+      <c r="F9" s="19"/>
     </row>
     <row r="10" ht="54" spans="1:6">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4" t="s">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="10">
         <v>23.2</v>
       </c>
-      <c r="F10" s="6"/>
+      <c r="F10" s="19"/>
     </row>
     <row r="11" ht="72" spans="1:6">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="10">
         <v>16.2</v>
       </c>
-      <c r="F11" s="6"/>
+      <c r="F11" s="19"/>
     </row>
     <row r="12" ht="36" spans="1:6">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="7" t="s">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="10">
         <v>16.5</v>
       </c>
-      <c r="F12" s="6"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" ht="36" spans="1:6">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="7" t="s">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="10">
         <v>16.1</v>
       </c>
-      <c r="F13" s="6"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" ht="54" spans="1:6">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="7"/>
+      <c r="C14" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="10">
         <v>7.4</v>
       </c>
-      <c r="F14" s="6"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" ht="36" spans="1:6">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4" t="s">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="10">
         <v>7.5</v>
       </c>
-      <c r="F15" s="6"/>
+      <c r="F15" s="19"/>
     </row>
     <row r="16" ht="36" spans="1:6">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="4" t="s">
+      <c r="B16" s="21"/>
+      <c r="C16" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="10">
         <v>19.3</v>
       </c>
-      <c r="F16" s="6"/>
+      <c r="F16" s="19"/>
     </row>
     <row r="17" ht="36" spans="1:6">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="4" t="s">
+      <c r="A17" s="22"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="10">
         <v>19.9</v>
       </c>
-      <c r="F17" s="6"/>
+      <c r="F17" s="19"/>
     </row>
     <row r="18" ht="36" spans="1:6">
-      <c r="A18" s="12"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="4" t="s">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="10">
         <v>19.1</v>
       </c>
-      <c r="F18" s="6"/>
+      <c r="F18" s="19"/>
     </row>
     <row r="19" ht="36" spans="1:6">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4" t="s">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="10">
         <v>15.1</v>
       </c>
-      <c r="F19" s="6"/>
+      <c r="F19" s="19"/>
     </row>
     <row r="20" ht="18" spans="1:6">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="6"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="19"/>
     </row>
     <row r="21" ht="18" spans="1:6">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4" t="s">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="6"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="19"/>
     </row>
     <row r="22" ht="18" spans="1:6">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4" t="s">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="6"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="19"/>
     </row>
     <row r="23" ht="18" spans="1:6">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4" t="s">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="6"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="19"/>
     </row>
     <row r="24" ht="36" spans="1:6">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4" t="s">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="6"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1847,4 +2020,675 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="7.31481481481481" customWidth="1"/>
+    <col min="2" max="2" width="36.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="25.4907407407407" customWidth="1"/>
+    <col min="4" max="4" width="26.0185185185185" customWidth="1"/>
+    <col min="5" max="5" width="19.7037037037037" style="1" customWidth="1"/>
+    <col min="6" max="6" width="29.3333333333333" customWidth="1"/>
+    <col min="7" max="7" width="30.712962962963" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17.4" spans="1:7">
+      <c r="A1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" ht="17.4" spans="1:7">
+      <c r="A2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" ht="17.4" spans="1:7">
+      <c r="A3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" ht="72" spans="1:7">
+      <c r="A4" s="5">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+    </row>
+    <row r="5" ht="72" spans="1:7">
+      <c r="A5" s="5">
+        <v>2</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+    </row>
+    <row r="6" ht="72" spans="1:7">
+      <c r="A6" s="5">
+        <v>3</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+    </row>
+    <row r="7" ht="72" spans="1:7">
+      <c r="A7" s="5">
+        <v>4</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="10">
+        <v>19.8</v>
+      </c>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+    </row>
+    <row r="8" ht="72" spans="1:7">
+      <c r="A8" s="5">
+        <v>5</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="10">
+        <v>19.8</v>
+      </c>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+    </row>
+    <row r="9" ht="54" spans="1:7">
+      <c r="A9" s="5">
+        <v>6</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="10">
+        <v>12.1</v>
+      </c>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+    </row>
+    <row r="10" ht="36" spans="1:7">
+      <c r="A10" s="5">
+        <v>7</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="10">
+        <v>12.2</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+    </row>
+    <row r="11" ht="90" spans="1:7">
+      <c r="A11" s="5">
+        <v>8</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+    </row>
+    <row r="12" ht="90" spans="1:7">
+      <c r="A12" s="5">
+        <v>9</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="10">
+        <v>8.3</v>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+    </row>
+    <row r="13" ht="90" spans="1:7">
+      <c r="A13" s="5">
+        <v>10</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="10">
+        <v>8.3</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+    </row>
+    <row r="14" ht="72" spans="1:7">
+      <c r="A14" s="5">
+        <v>11</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="10">
+        <v>8.2</v>
+      </c>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+    </row>
+    <row r="15" ht="17.4" spans="1:7">
+      <c r="A15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" ht="72" spans="1:7">
+      <c r="A16" s="5">
+        <v>12</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+    </row>
+    <row r="17" ht="72" spans="1:7">
+      <c r="A17" s="5">
+        <v>13</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+    </row>
+    <row r="18" ht="72" spans="1:7">
+      <c r="A18" s="5">
+        <v>14</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="8">
+        <v>7.1</v>
+      </c>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+    </row>
+    <row r="19" ht="72" spans="1:7">
+      <c r="A19" s="5">
+        <v>15</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="10">
+        <v>19.8</v>
+      </c>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+    </row>
+    <row r="20" ht="72" spans="1:7">
+      <c r="A20" s="5">
+        <v>16</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="10">
+        <v>19.8</v>
+      </c>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+    </row>
+    <row r="21" ht="90" spans="1:7">
+      <c r="A21" s="5">
+        <v>17</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+    </row>
+    <row r="22" ht="72" spans="1:7">
+      <c r="A22" s="5">
+        <v>18</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="10">
+        <v>8.2</v>
+      </c>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+    </row>
+    <row r="23" ht="180" spans="1:7">
+      <c r="A23" s="5">
+        <v>19</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+    </row>
+    <row r="24" ht="72" spans="1:7">
+      <c r="A24" s="5">
+        <v>20</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="10">
+        <v>16.1</v>
+      </c>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+    </row>
+    <row r="25" ht="90" spans="1:7">
+      <c r="A25" s="5">
+        <v>21</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="10">
+        <v>7.4</v>
+      </c>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+    </row>
+    <row r="26" ht="72" spans="1:7">
+      <c r="A26" s="5">
+        <v>22</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+    </row>
+    <row r="27" ht="72" spans="1:7">
+      <c r="A27" s="5">
+        <v>23</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+    </row>
+    <row r="28" ht="72" spans="1:7">
+      <c r="A28" s="5">
+        <v>24</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+    </row>
+    <row r="29" ht="72" spans="1:7">
+      <c r="A29" s="5">
+        <v>25</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+    </row>
+    <row r="30" ht="72" spans="1:7">
+      <c r="A30" s="5">
+        <v>26</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" s="10">
+        <v>19.9</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+    </row>
+    <row r="31" ht="54" spans="1:7">
+      <c r="A31" s="5">
+        <v>27</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="10">
+        <v>19.9</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+    </row>
+    <row r="32" ht="54" spans="1:7">
+      <c r="A32" s="5">
+        <v>28</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32" s="10">
+        <v>19.1</v>
+      </c>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+    </row>
+    <row r="33" ht="54" spans="1:7">
+      <c r="A33" s="5">
+        <v>29</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" s="10">
+        <v>19.1</v>
+      </c>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+    </row>
+    <row r="34" ht="54" spans="1:7">
+      <c r="A34" s="5">
+        <v>30</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="10">
+        <v>15.1</v>
+      </c>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+    </row>
+    <row r="35" ht="54" spans="1:7">
+      <c r="A35" s="5">
+        <v>31</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="10">
+        <v>15.1</v>
+      </c>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A15:G15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>